--- a/branches/fix/translation-cleanup/mii-cm-biobank-fixation-type-sprec-sct.xlsx
+++ b/branches/fix/translation-cleanup/mii-cm-biobank-fixation-type-sprec-sct.xlsx
@@ -54,7 +54,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-10T14:22:09+00:00</t>
+    <t>2026-09-10T14:28:13+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/fix/translation-cleanup/mii-cm-biobank-fixation-type-sprec-sct.xlsx
+++ b/branches/fix/translation-cleanup/mii-cm-biobank-fixation-type-sprec-sct.xlsx
@@ -54,7 +54,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-10T14:28:13+00:00</t>
+    <t>2026-09-10T14:44:18+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/fix/translation-cleanup/mii-cm-biobank-fixation-type-sprec-sct.xlsx
+++ b/branches/fix/translation-cleanup/mii-cm-biobank-fixation-type-sprec-sct.xlsx
@@ -54,7 +54,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-10T14:44:18+00:00</t>
+    <t>2026-09-10T14:50:34+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/fix/translation-cleanup/mii-cm-biobank-fixation-type-sprec-sct.xlsx
+++ b/branches/fix/translation-cleanup/mii-cm-biobank-fixation-type-sprec-sct.xlsx
@@ -54,7 +54,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-10T14:50:34+00:00</t>
+    <t>2026-09-10T14:57:02+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/fix/translation-cleanup/mii-cm-biobank-fixation-type-sprec-sct.xlsx
+++ b/branches/fix/translation-cleanup/mii-cm-biobank-fixation-type-sprec-sct.xlsx
@@ -54,7 +54,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-10T14:57:02+00:00</t>
+    <t>2026-09-10T15:20:02+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/fix/translation-cleanup/mii-cm-biobank-fixation-type-sprec-sct.xlsx
+++ b/branches/fix/translation-cleanup/mii-cm-biobank-fixation-type-sprec-sct.xlsx
@@ -54,7 +54,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-10T15:20:02+00:00</t>
+    <t>2026-09-10T15:26:35+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/fix/translation-cleanup/mii-cm-biobank-fixation-type-sprec-sct.xlsx
+++ b/branches/fix/translation-cleanup/mii-cm-biobank-fixation-type-sprec-sct.xlsx
@@ -54,7 +54,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-10T15:26:35+00:00</t>
+    <t>2026-09-10T15:38:34+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/fix/translation-cleanup/mii-cm-biobank-fixation-type-sprec-sct.xlsx
+++ b/branches/fix/translation-cleanup/mii-cm-biobank-fixation-type-sprec-sct.xlsx
@@ -54,7 +54,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-10T15:38:34+00:00</t>
+    <t>2026-09-10T15:45:44+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/fix/translation-cleanup/mii-cm-biobank-fixation-type-sprec-sct.xlsx
+++ b/branches/fix/translation-cleanup/mii-cm-biobank-fixation-type-sprec-sct.xlsx
@@ -54,7 +54,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-10T15:45:44+00:00</t>
+    <t>2026-09-10T15:57:48+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
